--- a/survey_templates/049_veneer_comfort_and_speech_survey--survey_templates.xlsx
+++ b/survey_templates/049_veneer_comfort_and_speech_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -854,29 +854,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>somewhat_uncomfortable</t>
+          <t>not_at_all_comfortable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Somewhat uncomfortable</t>
+          <t>Not at all comfortable</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>sensitivity_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_at_all_comfortable</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not at all comfortable</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mild</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mild</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -922,29 +922,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sensitivity_choices</t>
+          <t>speech_changes_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>severe</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Severe</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>slightly_changed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Slightly changed</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>slightly_changed</t>
+          <t>somewhat_changed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slightly changed</t>
+          <t>Somewhat changed</t>
         </is>
       </c>
     </row>
@@ -990,27 +990,10 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>somewhat_changed</t>
+          <t>significantly_changed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Somewhat changed</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>speech_changes_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>significantly_changed</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>Significantly changed</t>
         </is>
